--- a/config/yunying/rechargegift.xlsx
+++ b/config/yunying/rechargegift.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="rechargegift" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rechargegift" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -1282,7 +1282,6 @@
           <t>{20261=10;gold=60000;13=6}</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1312,7 +1311,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -1340,7 +1339,6 @@
           <t>{20261=10;gold=70000;13=6}</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1370,7 +1368,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -1398,7 +1396,6 @@
           <t>{20261=10;gold=80000;13=6}</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1428,7 +1425,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -1456,7 +1453,6 @@
           <t>{20261=10;gold=90000;13=6}</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1486,7 +1482,7 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -1521,18 +1517,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr"/>
       <c r="G9" s="1" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1562,7 +1548,7 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -1590,7 +1576,6 @@
           <t>{20011=10;gold=60000;13=6}</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1620,7 +1605,7 @@
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
@@ -1648,7 +1633,6 @@
           <t>{20011=10;gold=70000;13=6}</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1678,7 +1662,7 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -1706,7 +1690,6 @@
           <t>{20011=10;gold=80000;13=6}</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1736,7 +1719,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -1764,7 +1747,6 @@
           <t>{20011=10;gold=90000;13=6}</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1794,7 +1776,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -1829,18 +1811,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr"/>
       <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1870,7 +1842,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1898,7 +1870,6 @@
           <t>{20031=10;gold=60000;13=6}</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1928,7 +1899,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -1956,7 +1927,6 @@
           <t>{20031=10;gold=70000;13=6}</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1986,7 +1956,7 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -2014,7 +1984,6 @@
           <t>{20031=10;gold=80000;13=6}</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2044,7 +2013,7 @@
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -2072,7 +2041,6 @@
           <t>{20031=10;gold=90000;13=6}</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2102,7 +2070,7 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
@@ -2137,18 +2105,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="1" t="inlineStr"/>
       <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2178,7 +2136,7 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -2206,7 +2164,6 @@
           <t>{20591=10;516=6;gold=60000}</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2236,7 +2193,7 @@
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
@@ -2264,7 +2221,6 @@
           <t>{20591=10;516=6;gold=70000}</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2294,7 +2250,7 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
@@ -2322,7 +2278,6 @@
           <t>{20591=10;516=6;gold=80000}</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2352,7 +2307,7 @@
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
@@ -2380,7 +2335,6 @@
           <t>{20591=10;516=6;gold=90000}</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2410,7 +2364,7 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
@@ -2445,18 +2399,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr"/>
       <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2486,7 +2430,7 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -2514,7 +2458,6 @@
           <t>{21291=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2544,7 +2487,7 @@
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
@@ -2572,7 +2515,6 @@
           <t>{21291=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2602,7 +2544,7 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
@@ -2630,7 +2572,6 @@
           <t>{21291=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2660,7 +2601,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -2688,7 +2629,6 @@
           <t>{21291=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2718,7 +2658,7 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -2753,18 +2693,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr"/>
       <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2794,7 +2724,7 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -2822,7 +2752,6 @@
           <t>{21421=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2852,7 +2781,7 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -2880,7 +2809,6 @@
           <t>{21421=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2910,7 +2838,7 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -2938,7 +2866,6 @@
           <t>{21421=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2968,7 +2895,7 @@
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -2996,7 +2923,6 @@
           <t>{21421=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3026,7 +2952,7 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -3061,18 +2987,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr"/>
       <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3102,7 +3018,7 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -3130,7 +3046,6 @@
           <t>{21311=10;516=6;gold=60000}</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3160,7 +3075,7 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -3188,7 +3103,6 @@
           <t>{21311=10;516=6;gold=70000}</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3218,7 +3132,7 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
@@ -3246,7 +3160,6 @@
           <t>{21311=10;516=6;gold=80000}</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3276,7 +3189,7 @@
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
@@ -3304,7 +3217,6 @@
           <t>{21311=10;516=6;gold=90000}</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3334,7 +3246,7 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -3369,18 +3281,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr"/>
       <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3410,7 +3312,7 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -3438,7 +3340,6 @@
           <t>{20731=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3468,7 +3369,7 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -3496,7 +3397,6 @@
           <t>{20731=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3526,7 +3426,7 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -3554,7 +3454,6 @@
           <t>{20731=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3584,7 +3483,7 @@
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -3612,7 +3511,6 @@
           <t>{20731=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3642,7 +3540,7 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
@@ -3677,18 +3575,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr"/>
       <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3718,7 +3606,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -3746,7 +3634,6 @@
           <t>{23541=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3776,7 +3663,7 @@
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -3804,7 +3691,6 @@
           <t>{23541=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3834,7 +3720,7 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -3862,7 +3748,6 @@
           <t>{23541=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3892,7 +3777,7 @@
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -3920,7 +3805,6 @@
           <t>{23541=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3950,7 +3834,7 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -3985,18 +3869,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr"/>
       <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4026,7 +3900,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -4054,7 +3928,6 @@
           <t>{20391=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4084,7 +3957,7 @@
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
@@ -4112,7 +3985,6 @@
           <t>{20391=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4142,7 +4014,7 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -4170,7 +4042,6 @@
           <t>{20391=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4200,7 +4071,7 @@
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
@@ -4228,7 +4099,6 @@
           <t>{20391=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4258,7 +4128,7 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
@@ -4293,18 +4163,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" s="1" t="inlineStr"/>
       <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4334,7 +4194,7 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
@@ -4362,7 +4222,6 @@
           <t>{21241=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4392,7 +4251,7 @@
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
@@ -4420,7 +4279,6 @@
           <t>{21241=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4450,7 +4308,7 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
@@ -4478,7 +4336,6 @@
           <t>{21241=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4508,7 +4365,7 @@
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
@@ -4536,7 +4393,6 @@
           <t>{21241=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4566,7 +4422,7 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
@@ -4601,18 +4457,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" s="1" t="inlineStr"/>
       <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4642,7 +4488,7 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
@@ -4670,7 +4516,6 @@
           <t>{21391=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4700,7 +4545,7 @@
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
@@ -4728,7 +4573,6 @@
           <t>{21391=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4758,7 +4602,7 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
@@ -4786,7 +4630,6 @@
           <t>{21391=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4816,7 +4659,7 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
@@ -4844,7 +4687,6 @@
           <t>{21391=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4874,7 +4716,7 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
@@ -4909,18 +4751,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" s="1" t="inlineStr"/>
       <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4950,7 +4782,7 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
@@ -4978,7 +4810,6 @@
           <t>{20721=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5008,7 +4839,7 @@
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
@@ -5036,7 +4867,6 @@
           <t>{20721=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5066,7 +4896,7 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
@@ -5094,7 +4924,6 @@
           <t>{20721=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5124,7 +4953,7 @@
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
@@ -5152,7 +4981,6 @@
           <t>{20721=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5182,7 +5010,7 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
@@ -5217,18 +5045,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr"/>
       <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5258,7 +5076,7 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
@@ -5286,7 +5104,6 @@
           <t>{21231=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5316,7 +5133,7 @@
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
@@ -5344,7 +5161,6 @@
           <t>{21231=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5374,7 +5190,7 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
@@ -5402,7 +5218,6 @@
           <t>{21231=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5432,7 +5247,7 @@
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
@@ -5460,7 +5275,6 @@
           <t>{21231=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5490,7 +5304,7 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
@@ -5525,18 +5339,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr"/>
       <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5566,7 +5370,7 @@
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
@@ -5594,7 +5398,6 @@
           <t>{20601=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5624,7 +5427,7 @@
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
@@ -5652,7 +5455,6 @@
           <t>{20601=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5682,7 +5484,7 @@
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
@@ -5710,7 +5512,6 @@
           <t>{20601=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5740,7 +5541,7 @@
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
@@ -5768,7 +5569,6 @@
           <t>{20601=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5798,7 +5598,7 @@
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
@@ -5833,18 +5633,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr"/>
       <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5874,7 +5664,7 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
@@ -5902,7 +5692,6 @@
           <t>{20571=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5932,7 +5721,7 @@
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
@@ -5960,7 +5749,6 @@
           <t>{20571=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5990,7 +5778,7 @@
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
@@ -6018,7 +5806,6 @@
           <t>{20571=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6048,7 +5835,7 @@
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
@@ -6076,7 +5863,6 @@
           <t>{20571=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6106,7 +5892,7 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
@@ -6141,18 +5927,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr"/>
       <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6182,7 +5958,7 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
@@ -6210,7 +5986,6 @@
           <t>{20241=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6240,7 +6015,7 @@
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
@@ -6268,7 +6043,6 @@
           <t>{20241=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6298,7 +6072,7 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
@@ -6326,7 +6100,6 @@
           <t>{20241=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6356,7 +6129,7 @@
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
@@ -6384,7 +6157,6 @@
           <t>{20241=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6414,7 +6186,7 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
@@ -6449,18 +6221,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr"/>
       <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6490,7 +6252,7 @@
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
@@ -6518,7 +6280,6 @@
           <t>{20741=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6548,7 +6309,7 @@
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
@@ -6576,7 +6337,6 @@
           <t>{20741=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6606,7 +6366,7 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
@@ -6634,7 +6394,6 @@
           <t>{20741=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6664,7 +6423,7 @@
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
@@ -6692,7 +6451,6 @@
           <t>{20741=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6722,7 +6480,7 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
@@ -6757,18 +6515,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr"/>
       <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6798,7 +6546,7 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
@@ -6826,7 +6574,6 @@
           <t>{21081=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6856,7 +6603,7 @@
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
@@ -6884,7 +6631,6 @@
           <t>{21081=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6914,7 +6660,7 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
@@ -6942,7 +6688,6 @@
           <t>{21081=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6972,7 +6717,7 @@
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
@@ -7000,7 +6745,6 @@
           <t>{21081=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7030,7 +6774,7 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
@@ -7065,18 +6809,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr"/>
       <c r="G117" s="1" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7106,7 +6840,7 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
@@ -7134,7 +6868,6 @@
           <t>{21221=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7164,7 +6897,7 @@
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
@@ -7192,7 +6925,6 @@
           <t>{21221=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7222,7 +6954,7 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
@@ -7250,7 +6982,6 @@
           <t>{21221=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7280,7 +7011,7 @@
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
@@ -7308,7 +7039,6 @@
           <t>{21221=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7338,7 +7068,7 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
@@ -7373,18 +7103,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr"/>
       <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7414,7 +7134,7 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
@@ -7442,7 +7162,6 @@
           <t>{20491=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7472,7 +7191,7 @@
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
@@ -7500,7 +7219,6 @@
           <t>{20491=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7530,7 +7248,7 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
@@ -7558,7 +7276,6 @@
           <t>{20491=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7588,7 +7305,7 @@
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
@@ -7616,7 +7333,6 @@
           <t>{20491=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7646,7 +7362,7 @@
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
@@ -7681,18 +7397,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr"/>
       <c r="G129" s="1" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7722,7 +7428,7 @@
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
@@ -7750,7 +7456,6 @@
           <t>{21501=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7780,7 +7485,7 @@
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
@@ -7808,7 +7513,6 @@
           <t>{21501=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7838,7 +7542,7 @@
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
@@ -7866,7 +7570,6 @@
           <t>{21501=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7896,7 +7599,7 @@
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
@@ -7924,7 +7627,6 @@
           <t>{21501=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7954,7 +7656,7 @@
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
@@ -7989,18 +7691,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr"/>
       <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8030,7 +7722,7 @@
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
@@ -8058,7 +7750,6 @@
           <t>{23001=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8088,7 +7779,7 @@
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
@@ -8116,7 +7807,6 @@
           <t>{23001=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8146,7 +7836,7 @@
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
@@ -8174,7 +7864,6 @@
           <t>{23001=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8204,7 +7893,7 @@
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
@@ -8232,7 +7921,6 @@
           <t>{23001=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8262,7 +7950,7 @@
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
@@ -8297,18 +7985,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr"/>
       <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8338,7 +8016,7 @@
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
@@ -8366,7 +8044,6 @@
           <t>{21251=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8396,7 +8073,7 @@
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
@@ -8424,7 +8101,6 @@
           <t>{21251=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8454,7 +8130,7 @@
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
@@ -8482,7 +8158,6 @@
           <t>{21251=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8512,7 +8187,7 @@
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
@@ -8540,7 +8215,6 @@
           <t>{21251=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8570,7 +8244,7 @@
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
@@ -8605,18 +8279,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" s="1" t="inlineStr"/>
       <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8646,7 +8310,7 @@
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
@@ -8674,7 +8338,6 @@
           <t>{23021=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8704,7 +8367,7 @@
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
@@ -8732,7 +8395,6 @@
           <t>{23021=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8762,7 +8424,7 @@
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
@@ -8790,7 +8452,6 @@
           <t>{23021=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8820,7 +8481,7 @@
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
@@ -8848,7 +8509,6 @@
           <t>{23021=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8878,7 +8538,7 @@
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
@@ -8913,18 +8573,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" s="1" t="inlineStr"/>
       <c r="G153" s="1" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8954,7 +8604,7 @@
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
@@ -8982,7 +8632,6 @@
           <t>{20631=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9012,7 +8661,7 @@
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
@@ -9040,7 +8689,6 @@
           <t>{20631=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9070,7 +8718,7 @@
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
@@ -9098,7 +8746,6 @@
           <t>{20631=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9128,7 +8775,7 @@
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
@@ -9156,7 +8803,6 @@
           <t>{20631=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9186,7 +8832,7 @@
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
@@ -9221,18 +8867,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" s="1" t="inlineStr"/>
       <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9262,7 +8898,7 @@
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
@@ -9290,7 +8926,6 @@
           <t>{7400=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9320,7 +8955,7 @@
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
@@ -9348,7 +8983,6 @@
           <t>{7400=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9378,7 +9012,7 @@
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
@@ -9406,7 +9040,6 @@
           <t>{7400=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9436,7 +9069,7 @@
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
@@ -9464,7 +9097,6 @@
           <t>{7400=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9494,7 +9126,7 @@
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
@@ -9529,18 +9161,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" s="1" t="inlineStr"/>
       <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9570,7 +9192,7 @@
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
@@ -9598,7 +9220,6 @@
           <t>{7401=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9628,7 +9249,7 @@
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G167" s="1" t="inlineStr">
@@ -9656,7 +9277,6 @@
           <t>{7401=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9686,7 +9306,7 @@
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G168" s="1" t="inlineStr">
@@ -9714,7 +9334,6 @@
           <t>{7401=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9744,7 +9363,7 @@
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
@@ -9772,7 +9391,6 @@
           <t>{7401=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9802,7 +9420,7 @@
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
@@ -9837,18 +9455,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
-      <c r="B171" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" s="1" t="inlineStr"/>
       <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9878,7 +9486,7 @@
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G172" s="1" t="inlineStr">
@@ -9906,7 +9514,6 @@
           <t>{7402=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9936,7 +9543,7 @@
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G173" s="1" t="inlineStr">
@@ -9964,7 +9571,6 @@
           <t>{7402=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9994,7 +9600,7 @@
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G174" s="1" t="inlineStr">
@@ -10022,7 +9628,6 @@
           <t>{7402=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10052,7 +9657,7 @@
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G175" s="1" t="inlineStr">
@@ -10080,7 +9685,6 @@
           <t>{7402=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10110,7 +9714,7 @@
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G176" s="1" t="inlineStr">
@@ -10145,18 +9749,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" s="1" t="inlineStr"/>
       <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10186,7 +9780,7 @@
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G178" s="1" t="inlineStr">
@@ -10214,7 +9808,6 @@
           <t>{7403=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10244,7 +9837,7 @@
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G179" s="1" t="inlineStr">
@@ -10272,7 +9865,6 @@
           <t>{7403=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10302,7 +9894,7 @@
       </c>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G180" s="1" t="inlineStr">
@@ -10330,7 +9922,6 @@
           <t>{7403=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10360,7 +9951,7 @@
       </c>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G181" s="1" t="inlineStr">
@@ -10388,7 +9979,6 @@
           <t>{7403=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10418,7 +10008,7 @@
       </c>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G182" s="1" t="inlineStr">
@@ -10453,18 +10043,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
       <c r="F183" s="1" t="inlineStr"/>
       <c r="G183" s="1" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10494,7 +10074,7 @@
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G184" s="1" t="inlineStr">
@@ -10522,7 +10102,6 @@
           <t>{7404=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10552,7 +10131,7 @@
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G185" s="1" t="inlineStr">
@@ -10580,7 +10159,6 @@
           <t>{7404=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10610,7 +10188,7 @@
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G186" s="1" t="inlineStr">
@@ -10638,7 +10216,6 @@
           <t>{7404=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10668,7 +10245,7 @@
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G187" s="1" t="inlineStr">
@@ -10696,7 +10273,6 @@
           <t>{7404=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10726,7 +10302,7 @@
       </c>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G188" s="1" t="inlineStr">
@@ -10761,18 +10337,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr"/>
       <c r="G189" s="1" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10802,7 +10368,7 @@
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G190" s="1" t="inlineStr">
@@ -10830,7 +10396,6 @@
           <t>{7405=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10860,7 +10425,7 @@
       </c>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G191" s="1" t="inlineStr">
@@ -10888,7 +10453,6 @@
           <t>{7405=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10918,7 +10482,7 @@
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G192" s="1" t="inlineStr">
@@ -10946,7 +10510,6 @@
           <t>{7405=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10976,7 +10539,7 @@
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G193" s="1" t="inlineStr">
@@ -11004,7 +10567,6 @@
           <t>{7405=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11034,7 +10596,7 @@
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G194" s="1" t="inlineStr">
@@ -11062,21 +10624,10 @@
           <t>{card={id=9002};7405=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr"/>
       <c r="G195" s="1" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11106,7 +10657,7 @@
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G196" s="1" t="inlineStr">
@@ -11134,7 +10685,6 @@
           <t>{7406=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11164,7 +10714,7 @@
       </c>
       <c r="F197" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G197" s="1" t="inlineStr">
@@ -11192,7 +10742,6 @@
           <t>{7406=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11222,7 +10771,7 @@
       </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G198" s="1" t="inlineStr">
@@ -11250,7 +10799,6 @@
           <t>{7406=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11280,7 +10828,7 @@
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G199" s="1" t="inlineStr">
@@ -11308,7 +10856,6 @@
           <t>{7406=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11338,7 +10885,7 @@
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
@@ -11366,21 +10913,10 @@
           <t>{card={id=9002};7406=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
       <c r="F201" s="1" t="inlineStr"/>
       <c r="G201" s="1" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11410,7 +10946,7 @@
       </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G202" s="1" t="inlineStr">
@@ -11438,7 +10974,6 @@
           <t>{7407=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11468,7 +11003,7 @@
       </c>
       <c r="F203" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G203" s="1" t="inlineStr">
@@ -11496,7 +11031,6 @@
           <t>{7407=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11526,7 +11060,7 @@
       </c>
       <c r="F204" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G204" s="1" t="inlineStr">
@@ -11554,7 +11088,6 @@
           <t>{7407=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11584,7 +11117,7 @@
       </c>
       <c r="F205" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G205" s="1" t="inlineStr">
@@ -11612,7 +11145,6 @@
           <t>{7407=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11642,7 +11174,7 @@
       </c>
       <c r="F206" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G206" s="1" t="inlineStr">
@@ -11670,21 +11202,10 @@
           <t>{card={id=9002};7407=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" s="1" t="inlineStr"/>
       <c r="G207" s="1" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11714,7 +11235,7 @@
       </c>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G208" s="1" t="inlineStr">
@@ -11742,7 +11263,6 @@
           <t>{7408=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11772,7 +11292,7 @@
       </c>
       <c r="F209" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G209" s="1" t="inlineStr">
@@ -11800,7 +11320,6 @@
           <t>{7408=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11830,7 +11349,7 @@
       </c>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G210" s="1" t="inlineStr">
@@ -11858,7 +11377,6 @@
           <t>{7408=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11888,7 +11406,7 @@
       </c>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G211" s="1" t="inlineStr">
@@ -11916,7 +11434,6 @@
           <t>{7408=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11946,7 +11463,7 @@
       </c>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G212" s="1" t="inlineStr">
@@ -11974,21 +11491,10 @@
           <t>{card={id=9002};7408=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" s="1" t="inlineStr"/>
       <c r="G213" s="1" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12018,7 +11524,7 @@
       </c>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G214" s="1" t="inlineStr">
@@ -12046,7 +11552,6 @@
           <t>{7409=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12076,7 +11581,7 @@
       </c>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G215" s="1" t="inlineStr">
@@ -12104,7 +11609,6 @@
           <t>{7409=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12134,7 +11638,7 @@
       </c>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G216" s="1" t="inlineStr">
@@ -12162,7 +11666,6 @@
           <t>{7409=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12192,7 +11695,7 @@
       </c>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G217" s="1" t="inlineStr">
@@ -12220,7 +11723,6 @@
           <t>{7409=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12250,7 +11752,7 @@
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G218" s="1" t="inlineStr">
@@ -12278,21 +11780,10 @@
           <t>{card={id=9002};7409=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr"/>
       <c r="G219" s="1" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12322,7 +11813,7 @@
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G220" s="1" t="inlineStr">
@@ -12350,7 +11841,6 @@
           <t>{7410=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12380,7 +11870,7 @@
       </c>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G221" s="1" t="inlineStr">
@@ -12408,7 +11898,6 @@
           <t>{7410=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12438,7 +11927,7 @@
       </c>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G222" s="1" t="inlineStr">
@@ -12466,7 +11955,6 @@
           <t>{7410=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12496,7 +11984,7 @@
       </c>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G223" s="1" t="inlineStr">
@@ -12524,7 +12012,6 @@
           <t>{7410=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12554,7 +12041,7 @@
       </c>
       <c r="F224" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G224" s="1" t="inlineStr">
@@ -12582,21 +12069,10 @@
           <t>{card={id=9002};7410=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" s="1" t="inlineStr"/>
       <c r="G225" s="1" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12626,7 +12102,7 @@
       </c>
       <c r="F226" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G226" s="1" t="inlineStr">
@@ -12654,7 +12130,6 @@
           <t>{7411=10;2103=2;gold=60000}</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12684,7 +12159,7 @@
       </c>
       <c r="F227" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G227" s="1" t="inlineStr">
@@ -12712,7 +12187,6 @@
           <t>{7411=10;2103=2;gold=70000}</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12742,7 +12216,7 @@
       </c>
       <c r="F228" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G228" s="1" t="inlineStr">
@@ -12770,7 +12244,6 @@
           <t>{7411=10;2103=2;gold=80000}</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12800,7 +12273,7 @@
       </c>
       <c r="F229" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G229" s="1" t="inlineStr">
@@ -12828,7 +12301,6 @@
           <t>{7411=10;2103=2;gold=90000}</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12858,7 +12330,7 @@
       </c>
       <c r="F230" s="1" t="inlineStr">
         <is>
-          <t>計300ダイヤをチャージ</t>
+          <t>共充值300颗钻石</t>
         </is>
       </c>
       <c r="G230" s="1" t="inlineStr">
@@ -12886,7 +12358,6 @@
           <t>{card={id=9002};7411=10;2103=2;gold=100000}</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
